--- a/checklist_forms/033_dlp_incident_response_checklist--checklist_forms.xlsx
+++ b/checklist_forms/033_dlp_incident_response_checklist--checklist_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -442,7 +442,7 @@
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
     <col width="31" customWidth="1" min="2" max="2"/>
-    <col width="25" customWidth="1" min="3" max="3"/>
+    <col width="29" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
@@ -617,7 +617,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>If other please specify</t>
+          <t>Incident Type Other</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
@@ -755,7 +755,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>If other please specify</t>
+          <t>Incident Impact Other</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
@@ -801,7 +801,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>If other please specify</t>
+          <t>Incident Severity Other</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
@@ -842,12 +842,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>incident_responder</t>
+          <t>incident_responder_2</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Responder</t>
+          <t>Incident Responder 2</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
@@ -934,12 +934,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>incident_responder_note</t>
+          <t>incident_responder_note_2</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Responder notes</t>
+          <t>Incident Responder Note 2</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
@@ -957,7 +957,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>incident_responder_note_2</t>
+          <t>incident_responder_note_2_2</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -980,12 +980,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>incident_responder_note_2</t>
+          <t>incident_responder_note_2_3</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Responder notes 2</t>
+          <t>Incident Responder Note 2 3</t>
         </is>
       </c>
       <c r="D24" t="inlineStr"/>
@@ -1026,12 +1026,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>incident_responder_note_3</t>
+          <t>incident_responder_note_3_2</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Responder notes 3</t>
+          <t>Incident Responder Note 3 2</t>
         </is>
       </c>
       <c r="D26" t="inlineStr"/>
@@ -1072,12 +1072,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>incident_reviewed_by</t>
+          <t>incident_reviewed_by_2</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Reviewed By</t>
+          <t>Incident Reviewed By 2</t>
         </is>
       </c>
       <c r="D28" t="inlineStr"/>
@@ -1102,8 +1102,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="33" customWidth="1" min="1" max="1"/>
-    <col width="21" customWidth="1" min="2" max="2"/>
-    <col width="21" customWidth="1" min="3" max="3"/>
+    <col width="8" customWidth="1" min="2" max="2"/>
+    <col width="8" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1131,12 +1131,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'label':_'a'}</t>
+          <t>a</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'label': 'A'}</t>
+          <t>A</t>
         </is>
       </c>
     </row>
@@ -1148,12 +1148,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'label':_'b'}</t>
+          <t>b</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'label': 'B'}</t>
+          <t>B</t>
         </is>
       </c>
     </row>
@@ -1165,12 +1165,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'label':_'c'}</t>
+          <t>c</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'label': 'C'}</t>
+          <t>C</t>
         </is>
       </c>
     </row>
@@ -1182,12 +1182,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'label':_'a'}</t>
+          <t>a</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'label': 'A'}</t>
+          <t>A</t>
         </is>
       </c>
     </row>
@@ -1199,12 +1199,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'label':_'b'}</t>
+          <t>b</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'label': 'B'}</t>
+          <t>B</t>
         </is>
       </c>
     </row>
@@ -1216,12 +1216,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'label':_'c'}</t>
+          <t>c</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'label': 'C'}</t>
+          <t>C</t>
         </is>
       </c>
     </row>
@@ -1233,12 +1233,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'label':_'low'}</t>
+          <t>low</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'label': 'Low'}</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
@@ -1250,12 +1250,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'label':_'medium'}</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'label': 'Medium'}</t>
+          <t>Medium</t>
         </is>
       </c>
     </row>
@@ -1267,12 +1267,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'label':_'high'}</t>
+          <t>high</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'label': 'High'}</t>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -1284,12 +1284,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'label':_'low'}</t>
+          <t>low</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'label': 'Low'}</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
@@ -1301,12 +1301,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'label':_'medium'}</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'label': 'Medium'}</t>
+          <t>Medium</t>
         </is>
       </c>
     </row>
@@ -1318,12 +1318,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'label':_'high'}</t>
+          <t>high</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'label': 'High'}</t>
+          <t>High</t>
         </is>
       </c>
     </row>
